--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2024_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2024_magallanes.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 15:08</t>
+    <t xml:space="preserve">2026-09-24 01:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -576,13 +576,13 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.45</v>
+        <v>-0.29</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.19</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.61</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="3">
@@ -599,13 +599,13 @@
         <v>10</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.67</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.27</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="4">
@@ -622,13 +622,13 @@
         <v>10</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.31</v>
+        <v>-0.33</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.21</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.5</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="5">
@@ -645,13 +645,13 @@
         <v>10</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.71</v>
+        <v>-0.31</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.07</v>
+        <v>0.1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>-0.78</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="6">
@@ -668,13 +668,13 @@
         <v>10</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.27</v>
+        <v>0.52</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.13</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="7">
@@ -900,13 +900,13 @@
         <v>28</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.66</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.27</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="19">
@@ -923,13 +923,13 @@
         <v>30</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="20">
@@ -946,13 +946,13 @@
         <v>30</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0</v>
+        <v>0.07</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="21">
@@ -969,13 +969,13 @@
         <v>33</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.44</v>
+        <v>0.72</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.02</v>
+        <v>0.25</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="22">
@@ -992,13 +992,13 @@
         <v>33</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.57</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.31</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.09</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="23">
@@ -1015,13 +1015,13 @@
         <v>33</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.07</v>
+        <v>0.09</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="24">
@@ -1038,13 +1038,13 @@
         <v>10</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.54</v>
+        <v>-0.7</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.36</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="25">
@@ -1061,13 +1061,13 @@
         <v>10</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-0.56</v>
+        <v>-0.71</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-0.51</v>
+        <v>-0.53</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="26">
@@ -1084,13 +1084,13 @@
         <v>10</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-0.7</v>
+        <v>-0.79</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="27">
@@ -1107,13 +1107,13 @@
         <v>10</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-0.11</v>
+        <v>0.09</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>-0.44</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="28">
@@ -1130,13 +1130,13 @@
         <v>10</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.02</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="29">
@@ -1362,13 +1362,13 @@
         <v>28</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.43</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-0.66</v>
+        <v>-0.67</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.36</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="41">
@@ -1385,13 +1385,13 @@
         <v>30</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.26</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="42">
@@ -1408,13 +1408,13 @@
         <v>30</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.19</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="43">
@@ -1431,13 +1431,13 @@
         <v>33</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>-0.16</v>
+        <v>0.4</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>-0.28</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="44">
@@ -1454,13 +1454,13 @@
         <v>33</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.47</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.22</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.13</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="45">
@@ -1477,13 +1477,13 @@
         <v>33</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>0.06</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="46">
@@ -1893,13 +1893,13 @@
         <v>33</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0.09</v>
+        <v>-0.72</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.43</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.26</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="66">
@@ -1916,13 +1916,13 @@
         <v>33</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>0.16</v>
+        <v>0.79</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-0.15</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="67">
@@ -1939,13 +1939,13 @@
         <v>33</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>-0.01</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2024_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2024_magallanes.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:57</t>
+    <t xml:space="preserve">2026-10-01 23:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2024_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2024_magallanes.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:16</t>
+    <t xml:space="preserve">2026-10-05 20:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
